--- a/data/New Dataset/eval_data.xlsx
+++ b/data/New Dataset/eval_data.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,67 +429,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>srp</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ocp</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>isp</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>SRP_detections</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>OCP_detections</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LSP_detections</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ISP_detections</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>DIP_detections</t>
         </is>
@@ -4395,12 +4407,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4410,7 +4422,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4730,27 +4742,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4823,17 +4835,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5416,7 +5428,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5426,7 +5438,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5441,7 +5453,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5625,12 +5637,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5645,7 +5657,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5726,7 +5738,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5901,7 +5913,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6240,7 +6252,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6423,12 +6435,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6504,17 +6516,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6898,7 +6910,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -9825,7 +9837,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -10274,7 +10286,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -10697,7 +10709,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -12270,7 +12282,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -12359,7 +12371,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Violation</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -13362,7 +13374,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -14543,7 +14555,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -14628,7 +14640,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -14852,7 +14864,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Violation</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
